--- a/tests/fixtures/bulk_pricing_ahb_disk_test.xlsx
+++ b/tests/fixtures/bulk_pricing_ahb_disk_test.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Windows Server</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
